--- a/TrialRun.xlsx
+++ b/TrialRun.xlsx
@@ -17,16 +17,6 @@
     <sheet name="Books, page 8" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Books, page 9" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Books, page 10" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Books, page 11" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Books, page 12" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Books, page 13" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Books, page 14" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Books, page 15" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Books, page 16" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Books, page 17" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Books, page 18" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Books, page 19" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Books, page 20" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -958,2400 +948,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Dark Notes</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>£19.19</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Daring Greatly: How the Courage to Be Vulnerable Transforms the Way We Live, Love, Parent, and Lead</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>£19.43</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Close to You</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>£49.46</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Chasing Heaven: What Dying Taught Me About Living</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>£37.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Big Magic: Creative Living Beyond Fear</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>£30.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Becoming Wise: An Inquiry into the Mystery and Art of Living</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>£27.43</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Beauty Restored (Riley Family Legacy Novellas #3)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>£11.11</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Batman: The Long Halloween (Batman)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>£36.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Batman: The Dark Knight Returns (Batman)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>£15.38</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Ayumi's Violin</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>£15.48</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Anonymous</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>£46.82</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Amy Meets the Saints and Sages</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>£18.46</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Amid the Chaos</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>£36.58</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Amatus</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>£50.54</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Agnostic: A Spirited Manifesto</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>£12.51</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Zealot: The Life and Times of Jesus of Nazareth</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£24.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>You (You #1)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£43.61</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Wonder Woman: Earth One, Volume One (Wonder Woman: Earth One #1)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£37.34</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Wild Swans</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£14.36</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Why the Right Went Wrong: Conservatism--From Goldwater to the Tea Party and Beyond</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£52.65</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Whole Lotta Creativity Going On: 60 Fun and Unusual Exercises to Awaken and Strengthen Your Creativity</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>£38.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>What's It Like in Space?: Stories from Astronauts Who've Been There</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>£19.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>We Are Robin, Vol. 1: The Vigilante Business (We Are Robin #1)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>£53.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Walt Disney's Alice in Wonderland</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>£12.96</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>V for Vendetta (V for Vendetta Complete)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>£37.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Until Friday Night (The Field Party #1)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>£46.31</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Unbroken: A World War II Story of Survival, Resilience, and Redemption</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>£45.95</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Twenty Yawns</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>£22.08</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Through the Woods</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>£25.38</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>This Is Where It Ends</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>£27.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>The Year of Magical Thinking</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>£43.04</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>The Wright Brothers</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>£56.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>The White Queen (The Cousins' War #1)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>£25.91</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>The Wedding Pact (The O'Malleys #2)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>£32.61</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>The Time Keeper</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>£27.88</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>The Testament of Mary</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£52.67</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>The Star-Touched Queen</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£46.02</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>The Songs of the Gods</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£44.48</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>The Song of Achilles</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£37.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>The Rosie Project (Don Tillman #1)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£54.04</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>The Power of Habit: Why We Do What We Do in Life and Business</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>£16.88</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>The Marriage of Opposites</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>£28.08</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>The Lucifer Effect: Understanding How Good People Turn Evil</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>£10.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>The Long Haul (Diary of a Wimpy Kid #9)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>£44.07</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>The Loney</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>£23.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>The Literature Book (Big Ideas Simply Explained)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>£17.43</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>The Last Mile (Amos Decker #2)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>£54.21</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>The Immortal Life of Henrietta Lacks</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>£40.67</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>The Hidden Oracle (The Trials of Apollo #1)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>£52.26</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>The Help Yourself Cookbook for Kids: 60 Easy Plant-Based Recipes Kids Can Make to Stay Healthy and Save the Earth</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>£28.77</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>The Guilty (Will Robie #4)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>£13.82</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>The First Hostage (J.B. Collins #2)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>£25.85</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>The Dovekeepers</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>£48.78</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>The Darkest Lie</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>£35.35</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>The Bane Chronicles (The Bane Chronicles #1-11)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>£44.73</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>The Bad-Ass Librarians of Timbuktu: And Their Race to Save the World’s Most Precious Manuscripts</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£15.77</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>The 14th Colony (Cotton Malone #11)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£39.24</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>That Darkness (Gardiner and Renner #1)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£13.92</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Tastes Like Fear (DI Marnie Rome #3)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£10.69</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Take Me with You</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£45.21</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Swell: A Year of Waves</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>£45.58</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Superman Vol. 1: Before Truth (Superman by Gene Luen Yang #1)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>£11.89</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Still Life with Bread Crumbs</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>£26.41</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Steve Jobs</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>£39.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Sorting the Beef from the Bull: The Science of Food Fraud Forensics</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>£44.74</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Someone Like You (The Harrisons #2)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>£52.79</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>So Cute It Hurts!!, Vol. 6 (So Cute It Hurts!! #6)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>£35.43</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Shtum</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>£55.84</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>See America: A Celebration of Our National Parks &amp; Treasured Sites</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>£48.87</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>salt.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>£46.78</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Robin War</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>£47.82</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Red Hood/Arsenal, Vol. 1: Open for Business (Red Hood/Arsenal #1)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>£25.48</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Rain Fish</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>£23.57</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Quarter Life Poetry: Poems for the Young, Broke and Hangry</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>£50.89</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Pet Sematary</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>£10.56</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Overload: How to Unplug, Unwind, and Unleash Yourself from the Pressure of Stress</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£52.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Once Was a Time</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£18.28</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Old School (Diary of a Wimpy Kid #10)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£11.83</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>No Dream Is Too High: Life Lessons From a Man Who Walked on the Moon</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£21.95</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Naruto (3-in-1 Edition), Vol. 14: Includes Vols. 40, 41 &amp; 42 (Naruto: Omnibus #14)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£38.39</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>My Name Is Lucy Barton</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>£41.56</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>My Mrs. Brown</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>£24.48</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>My Kind of Crazy</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>£40.36</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Mr. Mercedes (Bill Hodges Trilogy #1)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>£28.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>More Than Music (Chasing the Dream #1)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>£37.61</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Made to Stick: Why Some Ideas Survive and Others Die</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>£38.85</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Luis Paints the World</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>£53.95</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Luckiest Girl Alive</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>£49.83</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Lowriders to the Center of the Earth (Lowriders in Space #2)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>£51.51</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Love Is a Mix Tape (Music #1)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>£18.03</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Looking for Lovely: Collecting the Moments that Matter</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>£29.14</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Living Leadership by Insight: A Good Leader Achieves, a Great Leader Builds Monuments</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>£46.91</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Let It Out: A Journey Through Journaling</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>£26.79</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Lady Midnight (The Dark Artifices #1)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>£16.28</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>It's All Easy: Healthy, Delicious Weeknight Meals in under 30 Minutes</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>£19.55</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Island of Dragons (Unwanteds #7)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£29.65</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>I Know What I'm Doing -- and Other Lies I Tell Myself: Dispatches from a Life Under Construction</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£25.98</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>I Am Pilgrim (Pilgrim #1)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£10.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Hyperbole and a Half: Unfortunate Situations, Flawed Coping Mechanisms, Mayhem, and Other Things That Happened</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£14.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Hush, Hush (Hush, Hush #1)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£47.02</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Hold Your Breath (Search and Rescue #1)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>£28.82</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Hamilton: The Revolution</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>£58.79</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Greek Mythic History</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>£10.23</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>God: The Most Unpleasant Character in All Fiction</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>£30.03</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Glory over Everything: Beyond The Kitchen House</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>£45.84</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Feathers: Displays of Brilliant Plumage</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>£49.05</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Far &amp; Away: Places on the Brink of Change: Seven Continents, Twenty-Five Years</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>£15.06</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Every Last Word</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>£46.47</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Eligible (The Austen Project #4)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>£27.09</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>El Deafo</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>£57.62</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Eight Hundred Grapes</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>£14.39</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Eaternity: More than 150 Deliciously Easy Vegan Recipes for a Long, Healthy, Satisfied, Joyful Life</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>£51.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Eat Fat, Get Thin</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>£54.07</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Don't Get Caught</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>£55.35</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Doctor Sleep (The Shining #2)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>£40.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Demigods &amp; Magicians: Percy and Annabeth Meet the Kanes (Percy Jackson &amp; Kane Chronicles Crossover #1-3)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£37.51</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Dear Mr. Knightley</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£11.21</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Daily Fantasy Sports</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£36.58</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Crazy Love: Overwhelmed by a Relentless God</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£47.72</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Cometh the Hour (The Clifton Chronicles #6)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£25.01</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Code Name Verity (Code Name Verity #1)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>£22.13</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Clockwork Angel (The Infernal Devices #1)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>£44.14</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>City of Glass (The Mortal Instruments #3)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>£56.02</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>City of Fallen Angels (The Mortal Instruments #4)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>£11.23</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>City of Bones (The Mortal Instruments #1)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>£43.28</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>City of Ashes (The Mortal Instruments #2)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>£47.27</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Cell</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>£20.29</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Catching Jordan (Hundred Oaks)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>£50.83</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Carry On, Warrior: Thoughts on Life Unarmed</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>£31.85</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Carrie</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>£46.23</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Buying In: The Secret Dialogue Between What We Buy and Who We Are</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>£37.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Brain on Fire: My Month of Madness</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>£49.32</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Batman: Europa</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>£32.01</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Barefoot Contessa Back to Basics</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>£28.01</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Barefoot Contessa at Home: Everyday Recipes You'll Make Over and Over Again</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>£50.62</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Balloon Animals</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£17.03</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Art Ops Vol. 1</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£48.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Aristotle and Dante Discover the Secrets of the Universe (Aristotle and Dante Discover the Secrets of the Universe #1)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£58.14</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Angels Walking (Angels Walking #1)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£34.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Angels &amp; Demons (Robert Langdon #1)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£51.48</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>All the Light We Cannot See</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>£29.87</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Adulthood Is a Myth: A "Sarah's Scribbles" Collection</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>£10.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Abstract City</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>£56.37</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A Time of Torment (Charlie Parker #14)</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>£48.35</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A Study in Scarlet (Sherlock Holmes #1)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>£16.73</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A Series of Catastrophes and Miracles: A True Story of Love, Science, and Cancer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>£56.48</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A People's History of the United States</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>£40.79</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A Man Called Ove</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>£39.72</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A Distant Mirror: The Calamitous 14th Century</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>£14.58</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A Brush of Wings (Angels Walking #3)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>£55.51</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>1491: New Revelations of the Americas Before Columbus</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>£21.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>The Three Searches, Meaning, and the Story</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>£13.33</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Searching for Meaning in Gailana</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>£38.73</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Rook</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>£37.86</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>My Kitchen Year: 136 Recipes That Saved My Life</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>£11.53</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>13 Hours: The Inside Account of What Really Happened In Benghazi</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£27.06</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Will You Won't You Want Me?</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£13.86</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Tipping Point for Planet Earth: How Close Are We to the Edge?</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£37.55</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>The Star-Touched Queen</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£32.30</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>The Silent Sister (Riley MacPherson #1)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£46.29</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>The Midnight Watch: A Novel of the Titanic and the Californian</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>£26.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>The Lonely City: Adventures in the Art of Being Alone</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>£33.26</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>The Gray Rhino: How to Recognize and Act on the Obvious Dangers We Ignore</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>£59.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>The Golden Condom: And Other Essays on Love Lost and Found</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>£39.43</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>The Epidemic (The Program 0.6)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>£14.44</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>The Dinner Party</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>£56.54</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>The Diary of a Young Girl</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>£59.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>The Children</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>£11.88</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Stars Above (The Lunar Chronicles #4.5)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>£48.05</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Snatched: How A Drug Queen Went Undercover for the DEA and Was Kidnapped By Colombian Guerillas</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>£21.21</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Raspberry Pi Electronics Projects for the Evil Genius</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>£49.67</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Quench Your Own Thirst: Business Lessons Learned Over a Beer or Two</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>£43.14</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Psycho: Sanitarium (Psycho #1.5)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>£36.97</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Poisonous (Max Revere Novels #3)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>£26.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>One with You (Crossfire #5)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>£15.71</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>No Love Allowed (Dodge Cove #1)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£54.65</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Murder at the 42nd Street Library (Raymond Ambler #1)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£54.36</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Most Wanted</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£35.28</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Love, Lies and Spies</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£20.55</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>How to Speak Golf: An Illustrated Guide to Links Lingo</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£58.32</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3610,272 +1206,6 @@
       <c r="B21" t="inlineStr">
         <is>
           <t>£33.63</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Hide Away (Eve Duncan #20)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>£11.84</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Furiously Happy: A Funny Book About Horrible Things</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>£41.46</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Everyday Italian: 125 Simple and Delicious Recipes</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>£20.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Equal Is Unfair: America's Misguided Fight Against Income Inequality</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>£56.86</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Eleanor &amp; Park</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>£56.51</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Dirty (Dive Bar #1)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>£40.83</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Can You Keep a Secret? (Fear Street Relaunch #4)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>£48.64</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Boar Island (Anna Pigeon #19)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>£59.48</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A Paris Apartment</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>£39.01</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A la Mode: 120 Recipes in 60 Pairings: Pies, Tarts, Cakes, Crisps, and More Topped with Ice Cream, Gelato, Frozen Custard, and More</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>£38.77</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Troublemaker: Surviving Hollywood and Scientology</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>£48.39</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>The Widow</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>£27.26</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>The Sleep Revolution: Transforming Your Life, One Night at a Time</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>£11.68</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>The Improbability of Love</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>£59.45</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>The Art of Startup Fundraising</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>£21.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Take Me Home Tonight (Rock Star Romance #3)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£53.98</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Sleeping Giants (Themis Files #1)</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£48.74</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Setting the World on Fire: The Brief, Astonishing Life of St. Catherine of Siena</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£21.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Playing with Fire</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£13.71</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Off the Hook (Fishing for Trouble #1)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£47.67</t>
         </is>
       </c>
     </row>

--- a/TrialRun.xlsx
+++ b/TrialRun.xlsx
@@ -12,11 +12,6 @@
     <sheet name="Books, page 3" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Books, page 4" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Books, page 5" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Books, page 6" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Books, page 7" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Books, page 8" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Books, page 9" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Books, page 10" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -682,272 +677,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Modern Romance</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>£28.26</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Miss Peregrine’s Home for Peculiar Children (Miss Peregrine’s Peculiar Children #1)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>£10.76</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Louisa: The Extraordinary Life of Mrs. Adams</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>£16.85</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Little Red</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>£13.47</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Library of Souls (Miss Peregrine’s Peculiar Children #3)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>£48.56</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Large Print Heart of the Pride</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>£19.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>I Had a Nice Time And Other Lies...: How to find love &amp; sh*t like that</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>£57.36</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Hollow City (Miss Peregrine’s Peculiar Children #2)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>£42.98</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Grumbles</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>£22.16</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Full Moon over Noah’s Ark: An Odyssey to Mount Ararat and Beyond</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>£49.43</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Frostbite (Vampire Academy #2)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>£29.99</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Follow You Home</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>£21.36</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>First Steps for New Christians (Print Edition)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>£29.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Finders Keepers (Bill Hodges Trilogy #2)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>£53.53</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Fables, Vol. 1: Legends in Exile (Fables #1)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>£41.62</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Eureka Trivia 6.0</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£54.59</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Drive: The Surprising Truth About What Motivates Us</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£34.95</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Done Rubbed Out (Reightman &amp; Bailey #1)</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£37.72</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Doing It Over (Most Likely To #1)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£35.61</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Deliciously Ella Every Day: Quick and Easy Recipes for Gluten-Free Snacks, Packed Lunches, and Simple Meals</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£42.16</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -2010,1068 +1739,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Immunity: How Elie Metchnikoff Changed the Course of Modern Medicine</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>£57.36</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>I Hate Fairyland, Vol. 1: Madly Ever After (I Hate Fairyland (Compilations) #1-5)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>£29.17</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>I am a Hero Omnibus Volume 1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>£54.63</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>How to Be Miserable: 40 Strategies You Already Use</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>£46.03</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Her Backup Boyfriend (The Sorensen Family #1)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>£33.97</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Giant Days, Vol. 2 (Giant Days #5-8)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>£22.11</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Forever and Forever: The Courtship of Henry Longfellow and Fanny Appleton</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>£29.69</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>First and First (Five Boroughs #3)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>£15.97</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Fifty Shades Darker (Fifty Shades #2)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>£21.96</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Everydata: The Misinformation Hidden in the Little Data You Consume Every Day</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>£54.35</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Don't Be a Jerk: And Other Practical Advice from Dogen, Japan's Greatest Zen Master</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>£37.97</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Danganronpa Volume 1</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>£51.99</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Crown of Midnight (Throne of Glass #2)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>£43.29</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Codename Baboushka, Volume 1: The Conclave of Death</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>£36.72</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Camp Midnight</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>£17.08</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Call the Nurse: True Stories of a Country Nurse on a Scottish Isle</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£29.14</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Burning</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£28.81</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Bossypants</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£49.46</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Bitch Planet, Vol. 1: Extraordinary Machine (Bitch Planet (Collected Editions))</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£37.92</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Avatar: The Last Airbender: Smoke and Shadow, Part 3 (Smoke and Shadow #3)</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£28.09</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Algorithms to Live By: The Computer Science of Human Decisions</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>£30.81</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A World of Flavor: Your Gluten Free Passport</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>£42.95</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A Piece of Sky, a Grain of Rice: A Memoir in Four Meditations</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>£56.76</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A Murder in Time</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>£16.64</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A Flight of Arrows (The Pathfinders #2)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>£55.53</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A Fierce and Subtle Poison</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>£28.13</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A Court of Thorns and Roses (A Court of Thorns and Roses #1)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>£52.37</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>(Un)Qualified: How God Uses Broken People to Do Big Things</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>£54.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>You Are What You Love: The Spiritual Power of Habit</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>£21.87</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>William Shakespeare's Star Wars: Verily, A New Hope (William Shakespeare's Star Wars #4)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>£43.30</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Tuesday Nights in 1980</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>£21.04</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Tracing Numbers on a Train</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>£41.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Throne of Glass (Throne of Glass #1)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>£35.07</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Thomas Jefferson and the Tripoli Pirates: The Forgotten War That Changed American History</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>£59.64</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Thirteen Reasons Why</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>£52.72</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>The White Cat and the Monk: A Retelling of the Poem “Pangur Bán”</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£58.08</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>The Wedding Dress</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£24.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>The Vacationers</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£42.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>The Third Wave: An Entrepreneur’s Vision of the Future</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£12.61</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>The Stranger</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£17.44</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>The Shadow Hero (The Shadow Hero)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>£33.14</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>The Secret (The Secret #1)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>£27.37</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>The Regional Office Is Under Attack!</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>£51.36</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>The Psychopath Test: A Journey Through the Madness Industry</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>£36.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>The Project</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>£10.65</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>The Power of Now: A Guide to Spiritual Enlightenment</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>£43.54</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>The Omnivore's Dilemma: A Natural History of Four Meals</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>£38.21</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>The Nerdy Nummies Cookbook: Sweet Treats for the Geek in All of Us</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>£37.34</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>The Murder of Roger Ackroyd (Hercule Poirot #4)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>£44.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>The Mistake (Off-Campus #2)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>£43.29</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>The Matchmaker's Playbook (Wingmen Inc. #1)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>£55.85</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>The Love and Lemons Cookbook: An Apple-to-Zucchini Celebration of Impromptu Cooking</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>£37.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>The Long Shadow of Small Ghosts: Murder and Memory in an American City</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>£10.97</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>The Kite Runner</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>£41.82</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>The House by the Lake</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>£36.95</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>The Glittering Court (The Glittering Court #1)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£44.28</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>The Girl on the Train</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£55.02</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>The Genius of Birds</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£17.24</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>The Emerald Mystery</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£23.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>The Cookies &amp; Cups Cookbook: 125+ sweet &amp; savory recipes reminding you to Always Eat Dessert First</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£41.25</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>The Bridge to Consciousness: I'm Writing the Bridge Between Science and Our Old and New Beliefs.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>£32.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>The Artist's Way: A Spiritual Path to Higher Creativity</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>£38.49</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>The Art of War</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>£33.34</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>The Argonauts</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>£10.93</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>The 10% Entrepreneur: Live Your Startup Dream Without Quitting Your Day Job</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>£27.55</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Suddenly in Love (Lake Haven #1)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>£55.99</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Something More Than This</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>£16.24</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Soft Apocalypse</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>£26.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>So You've Been Publicly Shamed</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>£12.23</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Shoe Dog: A Memoir by the Creator of NIKE</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>£23.99</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Shobu Samurai, Project Aryoku (#3)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>£29.06</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Secrets and Lace (Fatal Hearts #1)</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>£20.27</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Scarlett Epstein Hates It Here</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>£43.55</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Romero and Juliet: A Tragic Tale of Love and Zombies</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>£36.94</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Redeeming Love</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>£20.47</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Poses for Artists Volume 1 - Dynamic and Sitting Poses: An Essential Reference for Figure Drawing and the Human Form</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>£41.06</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Poems That Make Grown Women Cry</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>£14.19</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Nightingale, Sing</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>£38.28</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Night Sky with Exit Wounds</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>£41.05</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Mrs. Houdini</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>£30.25</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>